--- a/buoi_11_baihoc/data/user_information.xlsx
+++ b/buoi_11_baihoc/data/user_information.xlsx
@@ -466,16 +466,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>37472</v>
+        <v>46300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pddat@cybersoft.edu.vn</t>
+          <t>29e8@gmal.co</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0902850103</t>
+          <t>0902472477</t>
         </is>
       </c>
       <c r="E2" t="b">
